--- a/data/actuator_requirements.xlsx
+++ b/data/actuator_requirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\scripts\hil\hil-test-case-gen\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79A8F2C-7C55-450D-8131-C91A24B22692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552E6287-CA42-4F22-B77E-63BD7FFFFDC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{4E185E56-D21A-4CEB-9BC3-DCDD147047F3}"/>
   </bookViews>
@@ -38,51 +38,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
-    <t>If a brake actuator fault is detected, the system shall limit vehicle speed to a predefined safe limit until corrective actions are undertaken.</t>
-  </si>
-  <si>
-    <t>The BBW system shall engage the mechanical fallback if the primary braking actuator fails to respond correctly.</t>
-  </si>
-  <si>
-    <t>The ACC shall automatically disable control and revert to manual driving in case of engine actuator failure to avoid unintended acceleration.</t>
-  </si>
-  <si>
-    <t>The braking actuator shall be capable of engaging regenerative braking processes in case of hydraulic brake failure to maintain vehicle control.</t>
-  </si>
-  <si>
-    <t>The ACC will ensure limited but consistent functionality when faced with a partial failure of the steering actuator to maintain basic maneuverability.</t>
-  </si>
-  <si>
-    <t>In the event of a detected actuator overage (e.g., over a predefined limit of travel or force), the system shall disengage the affected control and alert the driver.</t>
-  </si>
-  <si>
-    <t>In case of motor overheating in the steering actuator, the system shall reduce electrical current to the actuator to maintain functionality within safe thermal conditions while notifying the driver.</t>
-  </si>
-  <si>
-    <t>If the throttle actuator fails, the system shall immediately reduce throttle opening to achieve engine idle position and provide driver notification through the instrument panel.</t>
-  </si>
-  <si>
-    <t>The electronic throttle control actuator shall incorporate fault detection algorithms to identify and rectify position sensor discrepancies within 50 milliseconds.</t>
-  </si>
-  <si>
     <t>In the event of simultaneous failures in both the throttle and brake actuators, the system shall activate an emergency deceleration procedure and automatically engage hazard lights.</t>
   </si>
   <si>
-    <t>The vehicle system shall verify successful engagement of the EPB actuator after each parking brake application and notify the driver of any anomalies.</t>
-  </si>
-  <si>
-    <t>The system must automatically disengage the steering actuator from active control whenever a significant torque discrepancy is detected between input and output for more than 300 milliseconds.</t>
-  </si>
-  <si>
-    <t>The engine control actuator must transition into a limp-home mode restricting engine output if throttle position sensors within the actuator system detect a fault lasting more than 200 milliseconds.</t>
-  </si>
-  <si>
-    <t>The engine actuator's fuel and ignition systems shall autonomously reduce power output to idle conditions in the event of communication loss with the main control unit.</t>
-  </si>
-  <si>
-    <t>In the event of failed actuator communication within the transmission system, the drivetrain must limit gear selection options to predefined safe gears and inform the driver.</t>
-  </si>
-  <si>
     <t>If brake pressure verification fails to meet command criteria, the system must limit vehicle speed and provide driver notification.</t>
   </si>
   <si>
@@ -101,18 +59,9 @@
     <t>On detecting stepper motor faults, the system shall disable automatic lane change functionality immediately, requiring manual verification by the driver before proceeding.</t>
   </si>
   <si>
-    <t>On braking actuator failure detection, ACC shall immediately switch to manual driving mode within 1 second, issuing both a visual warning on the dashboard and an auditory alert to the driver.</t>
-  </si>
-  <si>
     <t>In cases of conflicting inputs from failed actuators (e.g., unintended throttle and braking), the system prioritizes braking to ensure vehicle deceleration.</t>
   </si>
   <si>
-    <t>All actuator signal processes must be isolated with a noise rejection threshold of ±2% to prevent interference from auxiliary electronic systems.</t>
-  </si>
-  <si>
-    <t>Emergency stop mechanisms shall be triggered within 0.1 seconds of dual actuator (throttle and brake) failures to prevent uncontrollable vehicle acceleration.</t>
-  </si>
-  <si>
     <t>The ACC shall automatically revert to manual control in the event of actuator-related circuit shorts to maintain safe vehicle operation.</t>
   </si>
   <si>
@@ -122,22 +71,73 @@
     <t>Engine system shall limit the throttle-angle for an applicable time if the current vehicle acceleration is higher than the target vehicle acceleration.</t>
   </si>
   <si>
-    <t>On actuator failure detection, ACC shall immediately switch to manual driving mode within 1 second, issuing both a visual warning on the dashboard and an auditory alert to the driver.</t>
-  </si>
-  <si>
     <t>The vehicle shall enter a limp-home mode that restricts its speed to 30 km/h if stepper motor malfunctions persistently affect lane-keeping abilities, to ensure road safety.</t>
   </si>
   <si>
-    <t>Emergency stop protocols must be triggers within 0.1 seconds of simultaneous actuator failures affecting braking or acceleration.</t>
-  </si>
-  <si>
     <t>Actuator-driven changes to vehicle speed and following distances shall remain within established emergency parameters (e.g., maximum deceleration of -3 m/s²) when faults are detected.</t>
   </si>
   <si>
-    <t>Regular updates to the ACC system involving actuator management strategies must pass rigorous testing under defined failure modes before deployment.</t>
-  </si>
-  <si>
     <t>Requirement</t>
+  </si>
+  <si>
+    <t>If a brake fault is detected, the system shall limit vehicle speed to a predefined safe limit until corrective actions are undertaken.</t>
+  </si>
+  <si>
+    <t>The BBW system shall engage the mechanical fallback if the primary braking fails to respond correctly.</t>
+  </si>
+  <si>
+    <t>The ACC shall automatically disable control and revert to manual driving in case of engine failure to avoid unintended acceleration.</t>
+  </si>
+  <si>
+    <t>The braking shall be capable of engaging regenerative braking processes in case of hydraulic brake failure to maintain vehicle control.</t>
+  </si>
+  <si>
+    <t>The ACC will ensure limited but consistent functionality when faced with a partial failure of the steering to maintain basic maneuverability.</t>
+  </si>
+  <si>
+    <t>In the event of a detected overage (e.g., over a predefined limit of travel or force), the system shall disengage the affected control and alert the driver.</t>
+  </si>
+  <si>
+    <t>If the throttle fails, the system shall immediately reduce throttle opening to achieve engine idle position and provide driver notification through the instrument panel.</t>
+  </si>
+  <si>
+    <t>The electronic throttle control shall incorporate fault detection algorithms to identify and rectify position sensor discrepancies within 50 milliseconds.</t>
+  </si>
+  <si>
+    <t>The vehicle system shall verify successful engagement of the EPB after each parking brake application and notify the driver of any anomalies.</t>
+  </si>
+  <si>
+    <t>The system must automatically disengage the steering from active control whenever a significant torque discrepancy is detected between input and output for more than 300 milliseconds.</t>
+  </si>
+  <si>
+    <t>The engine control must transition into a limp-home mode restricting engine output if throttle position sensors within the system detect a fault lasting more than 200 milliseconds.</t>
+  </si>
+  <si>
+    <t>In the event of failed communication within the transmission system, the drivetrain must limit gear selection options to predefined safe gears and inform the driver.</t>
+  </si>
+  <si>
+    <t>Regular updates to the ACC system involving management strategies must pass rigorous testing under defined failure modes before deployment.</t>
+  </si>
+  <si>
+    <t>Emergency stop mechanisms shall be triggered within 0.1 seconds of dual (throttle and brake) failures to prevent uncontrollable vehicle acceleration.</t>
+  </si>
+  <si>
+    <t>On braking failure detection, ACC shall immediately switch to manual driving mode within 1 second, issuing both a visual warning on the dashboard and an auditory alert to the driver.</t>
+  </si>
+  <si>
+    <t>All signal processes must be isolated with a noise rejection threshold of ±2% to prevent interference from auxiliary electronic systems.</t>
+  </si>
+  <si>
+    <t>On failure detection, ACC shall immediately switch to manual driving mode within 1 second, issuing both a visual warning on the dashboard and an auditory alert to the driver.</t>
+  </si>
+  <si>
+    <t>Emergency stop protocols must be triggers within 0.1 seconds of simultaneous failures affecting braking or acceleration.</t>
+  </si>
+  <si>
+    <t>The engine fuel and ignition systems shall autonomously reduce power output to idle conditions in the event of communication loss with the main control unit.</t>
+  </si>
+  <si>
+    <t>In case of motor overheating in the steering, the system shall reduce electrical current to the to maintain functionality within safe thermal conditions while notifying the driver.</t>
   </si>
 </sst>
 </file>
@@ -250,10 +250,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{64DC391B-C710-49AD-963E-B5A7F18F53EA}" name="Table1" displayName="Table1" ref="A1:A38" totalsRowShown="0" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{64DC391B-C710-49AD-963E-B5A7F18F53EA}" name="Table1" displayName="Table1" ref="A1:A38" totalsRowShown="0" dataDxfId="1">
   <autoFilter ref="A1:A38" xr:uid="{64DC391B-C710-49AD-963E-B5A7F18F53EA}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{F09C1E09-4A34-4989-9307-563E5DF52BC9}" name="Requirement" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{F09C1E09-4A34-4989-9307-563E5DF52BC9}" name="Requirement" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -584,192 +584,192 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="1" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.55000000000000004">
